--- a/l1.xlsx
+++ b/l1.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,33 @@
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>تم بواسطه</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>تم تركيب</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>تم التشغيل</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1\2\2024</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>م.عبدالرحمن صيام</t>
         </is>
       </c>
     </row>

--- a/l1.xlsx
+++ b/l1.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="BOP" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="clx1" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -499,4 +500,45 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>رقم الماكينه</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>الحدث</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>التصحيح</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>تم بواسطه</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l1.xlsx
+++ b/l1.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="BOP" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="clx1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="clx2" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -541,4 +542,45 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>رقم الماكينه</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>الحدث</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>التصحيح</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>تم بواسطه</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l1.xlsx
+++ b/l1.xlsx
@@ -11,6 +11,7 @@
     <sheet name="BOP" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="clx1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="clx2" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="سحب1" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -583,4 +584,45 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>رقم الماكينه</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>تم بواسطه</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>الحدث</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>التصحيح</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>عدد اطنان</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l1.xlsx
+++ b/l1.xlsx
@@ -12,6 +12,7 @@
     <sheet name="clx1" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="clx2" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="سحب1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="تمشيط 1" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -625,4 +626,45 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>رقم الماكينه</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>تم بواسطه</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>الحدث</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>التصحيح</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>عدد اطنان</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l1.xlsx
+++ b/l1.xlsx
@@ -13,6 +13,7 @@
     <sheet name="clx2" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="سحب1" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="تمشيط 1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="تمشيط 2" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -667,4 +668,45 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>رقم الماكينه</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>تم بواسطه</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>الحدث</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>التصحيح</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>عدد اطنان</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l1.xlsx
+++ b/l1.xlsx
@@ -14,6 +14,7 @@
     <sheet name="سحب1" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="تمشيط 1" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="تمشيط 2" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="تمشيط 3" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -709,4 +710,45 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>رقم الماكينه</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>تم بواسطه</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>الحدث</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>التصحيح</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>عدد اطنان</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l1.xlsx
+++ b/l1.xlsx
@@ -15,6 +15,7 @@
     <sheet name="تمشيط 1" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="تمشيط 2" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="تمشيط 3" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="سحب 3" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -751,4 +752,45 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>رقم الماكينه</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>تم بواسطه</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>الحدث</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>التصحيح</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>عدد اطنان</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l1.xlsx
+++ b/l1.xlsx
@@ -16,6 +16,7 @@
     <sheet name="تمشيط 2" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="تمشيط 3" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="سحب 3" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="سحب2" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,13 +441,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E2"/>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,49 +458,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>تم بواسطه</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>الحدث</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>التصحيح</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>تم بواسطه</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>تم تركيب</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>تم التشغيل</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1\2\2024</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>م.عبدالرحمن صيام</t>
+          <t>عدد اطنان</t>
         </is>
       </c>
     </row>
@@ -508,13 +482,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,12 +509,39 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>تم بواسطه</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>التاريخ</t>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>تم تركيب</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>تم التشغيل</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1\2\2024</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>م.عبدالرحمن صيام</t>
         </is>
       </c>
     </row>
@@ -549,7 +550,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -590,7 +591,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -607,22 +608,22 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>الحدث</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>التصحيح</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>تم بواسطه</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>الحدث</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>التصحيح</t>
-        </is>
-      </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>عدد اطنان</t>
+          <t>التاريخ</t>
         </is>
       </c>
     </row>
@@ -631,7 +632,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -672,7 +673,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -713,7 +714,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -754,7 +755,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -793,4 +794,45 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>رقم الماكينه</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>تم بواسطه</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>الحدث</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>التصحيح</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>عدد اطنان</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/l1.xlsx
+++ b/l1.xlsx
@@ -17,6 +17,7 @@
     <sheet name="تمشيط 3" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="سحب 3" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="سحب2" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="تحضيرات كرد" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,16 +27,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -46,7 +44,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -54,21 +52,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -451,27 +440,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>رقم الماكينه</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>تم بواسطه</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>الحدث</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>التصحيح</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>عدد اطنان</t>
         </is>
@@ -482,6 +471,62 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>التاريخ</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>المعدة</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>الحدث/العطل</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>الإجراء التصحيحي</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>تم بواسطة</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>الطن</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>الصور</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ملاحظات</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -492,27 +537,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>رقم الماكينه</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>الحدث</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>التصحيح</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>التاريخ</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>تم بواسطه</t>
         </is>
@@ -560,27 +605,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>رقم الماكينه</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>الحدث</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>التصحيح</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>تم بواسطه</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>التاريخ</t>
         </is>
@@ -601,27 +646,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>رقم الماكينه</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>الحدث</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>التصحيح</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>تم بواسطه</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>التاريخ</t>
         </is>
@@ -642,27 +687,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>رقم الماكينه</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>تم بواسطه</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>الحدث</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>التصحيح</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>عدد اطنان</t>
         </is>
@@ -683,27 +728,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>رقم الماكينه</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>تم بواسطه</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>الحدث</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>التصحيح</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>عدد اطنان</t>
         </is>
@@ -724,27 +769,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>رقم الماكينه</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>تم بواسطه</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>الحدث</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>التصحيح</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>عدد اطنان</t>
         </is>
@@ -765,27 +810,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>رقم الماكينه</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>تم بواسطه</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>الحدث</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>التصحيح</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>عدد اطنان</t>
         </is>
@@ -806,27 +851,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>رقم الماكينه</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>تم بواسطه</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>الحدث</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>التصحيح</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>عدد اطنان</t>
         </is>
